--- a/data/trans_orig/Q25B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar</t>
+          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar (tasa de respuesta: 96,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 14,42</t>
+          <t>7,88; 14,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,62</t>
+          <t>9,9; 19,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,0</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,32</t>
+          <t>7,17; 14,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 16,52</t>
+          <t>7,41; 16,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 13,79</t>
+          <t>7,51; 13,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,46</t>
+          <t>6,37; 14,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,24</t>
+          <t>8,36; 13,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 15,91</t>
+          <t>9,41; 15,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,51</t>
+          <t>7,63; 12,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,45</t>
+          <t>3,87; 11,54</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,66</t>
+          <t>13,16; 17,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,01; 19,89</t>
+          <t>14,04; 20,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 15,32</t>
+          <t>11,03; 15,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 15,1</t>
+          <t>6,1; 14,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,44</t>
+          <t>8,99; 11,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,41</t>
+          <t>9,57; 13,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,52</t>
+          <t>8,99; 12,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,26</t>
+          <t>5,27; 9,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 13,37</t>
+          <t>10,85; 13,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,84</t>
+          <t>12,27; 15,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,18</t>
+          <t>10,49; 13,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,39</t>
+          <t>6,5; 10,76</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,87</t>
+          <t>18,82; 23,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,2</t>
+          <t>16,68; 21,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 19,33</t>
+          <t>14,37; 19,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,68</t>
+          <t>13,17; 20,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,42</t>
+          <t>9,57; 14,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,03</t>
+          <t>12,42; 17,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 15,84</t>
+          <t>11,89; 15,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,97</t>
+          <t>8,59; 12,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 18,91</t>
+          <t>15,24; 18,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,98; 18,13</t>
+          <t>15,07; 18,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 16,91</t>
+          <t>13,54; 16,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,99</t>
+          <t>11,23; 15,09</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 21,65</t>
+          <t>17,43; 21,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 24,38</t>
+          <t>20,41; 24,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 26,7</t>
+          <t>20,9; 26,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 22,66</t>
+          <t>18,01; 22,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 17,97</t>
+          <t>12,45; 18,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 16,07</t>
+          <t>12,17; 15,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,58</t>
+          <t>12,24; 16,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 13,52</t>
+          <t>10,55; 13,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 19,72</t>
+          <t>16,39; 19,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 21,11</t>
+          <t>17,93; 21,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,51; 21,38</t>
+          <t>17,63; 21,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 19,92</t>
+          <t>16,25; 19,99</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,2; 28,09</t>
+          <t>23,38; 28,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 27,76</t>
+          <t>22,51; 28,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,96; 26,46</t>
+          <t>21,0; 26,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,12; 22,8</t>
+          <t>19,07; 22,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 21,19</t>
+          <t>13,58; 21,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,62</t>
+          <t>10,92; 17,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,66</t>
+          <t>12,17; 17,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 15,66</t>
+          <t>12,45; 15,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,57; 26,94</t>
+          <t>22,6; 26,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,02; 24,64</t>
+          <t>19,78; 24,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 23,31</t>
+          <t>18,71; 23,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 19,9</t>
+          <t>17,12; 19,64</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,53; 26,92</t>
+          <t>22,55; 26,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,5; 32,41</t>
+          <t>25,95; 32,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,52; 26,83</t>
+          <t>21,23; 26,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,29; 26,42</t>
+          <t>22,13; 26,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,69</t>
+          <t>10,74; 22,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,67</t>
+          <t>9,38; 18,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 19,27</t>
+          <t>10,1; 19,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,03; 17,37</t>
+          <t>11,65; 17,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 25,84</t>
+          <t>21,64; 25,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,58; 31,73</t>
+          <t>25,6; 31,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,45</t>
+          <t>19,66; 24,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,85</t>
+          <t>20,23; 23,93</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,73; 27,06</t>
+          <t>21,81; 27,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 25,99</t>
+          <t>21,2; 26,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,35; 25,57</t>
+          <t>20,46; 25,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,66; 22,37</t>
+          <t>18,54; 22,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 19,27</t>
+          <t>9,56; 19,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,93</t>
+          <t>7,05; 17,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,42; 22,95</t>
+          <t>13,07; 22,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,21; 26,53</t>
+          <t>21,08; 25,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,64; 25,19</t>
+          <t>20,81; 25,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,35; 25,41</t>
+          <t>20,44; 25,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,06</t>
+          <t>18,43; 21,98</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,44</t>
+          <t>21,36; 23,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,11; 24,47</t>
+          <t>22,08; 24,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,54; 22,83</t>
+          <t>20,51; 22,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,74; 21,45</t>
+          <t>19,77; 21,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,83</t>
+          <t>11,64; 13,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,62</t>
+          <t>12,44; 14,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,4</t>
+          <t>12,41; 14,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,11</t>
+          <t>11,39; 13,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,4</t>
+          <t>18,81; 20,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 21,0</t>
+          <t>19,14; 20,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,81; 19,62</t>
+          <t>17,66; 19,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,18</t>
+          <t>17,36; 19,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>7,18</t>
         </is>
       </c>
     </row>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,53</t>
+          <t>7,84; 14,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 19,14</t>
+          <t>9,84; 18,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,16</t>
+          <t>5,04; 14,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 14,07</t>
+          <t>7,1; 14,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 16,76</t>
+          <t>7,66; 17,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,58</t>
+          <t>7,75; 13,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 14,23</t>
+          <t>5,43; 13,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 13,39</t>
+          <t>8,28; 13,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 15,92</t>
+          <t>9,66; 15,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,81</t>
+          <t>7,49; 12,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 11,54</t>
+          <t>4,15; 11,24</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>8,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,77</t>
+          <t>12,97; 17,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 20,05</t>
+          <t>13,89; 19,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 15,28</t>
+          <t>10,94; 15,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 14,57</t>
+          <t>5,29; 13,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 11,3</t>
+          <t>8,86; 11,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,43</t>
+          <t>9,87; 13,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,37</t>
+          <t>8,85; 12,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,32</t>
+          <t>5,7; 11,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 13,24</t>
+          <t>10,87; 13,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 15,64</t>
+          <t>12,11; 15,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,13</t>
+          <t>10,38; 13,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,76</t>
+          <t>6,4; 10,97</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,15</t>
+          <t>16,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,94</t>
+          <t>12,99</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,4</t>
+          <t>18,69; 23,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 21,11</t>
+          <t>16,76; 21,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,25</t>
+          <t>14,57; 19,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 20,01</t>
+          <t>13,48; 19,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 14,47</t>
+          <t>9,87; 14,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,25</t>
+          <t>12,47; 17,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 15,69</t>
+          <t>11,97; 15,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,16</t>
+          <t>8,72; 12,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,24; 18,65</t>
+          <t>15,17; 18,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 18,37</t>
+          <t>15,04; 18,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 16,77</t>
+          <t>13,65; 16,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,09</t>
+          <t>11,33; 15,04</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>12,17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,63</t>
+          <t>16,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 21,95</t>
+          <t>17,57; 21,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 24,46</t>
+          <t>20,55; 24,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 26,78</t>
+          <t>20,99; 26,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 22,71</t>
+          <t>18,15; 23,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 18,32</t>
+          <t>12,46; 18,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,17; 15,91</t>
+          <t>12,28; 16,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,5</t>
+          <t>12,46; 16,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,48</t>
+          <t>10,82; 13,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,92</t>
+          <t>16,36; 19,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 21,16</t>
+          <t>18,06; 21,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 21,43</t>
+          <t>17,54; 21,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 19,99</t>
+          <t>15,36; 18,64</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>20,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,36</t>
+          <t>18,25</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,38; 28,14</t>
+          <t>23,36; 28,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,11</t>
+          <t>22,1; 28,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,0; 26,72</t>
+          <t>21,1; 26,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 22,68</t>
+          <t>19,04; 22,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 21,48</t>
+          <t>13,45; 21,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 17,07</t>
+          <t>10,88; 16,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 17,75</t>
+          <t>12,15; 17,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 15,71</t>
+          <t>12,28; 15,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,6; 26,96</t>
+          <t>22,56; 27,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,29</t>
+          <t>19,67; 24,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,17</t>
+          <t>18,54; 23,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 19,64</t>
+          <t>16,88; 19,68</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,19</t>
+          <t>23,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>15,11</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,04</t>
+          <t>22,03</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,55; 26,98</t>
+          <t>22,51; 26,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,95; 32,28</t>
+          <t>26,36; 32,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 26,93</t>
+          <t>21,48; 26,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,13; 26,18</t>
+          <t>22,05; 25,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 22,26</t>
+          <t>10,53; 21,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,38; 18,66</t>
+          <t>9,63; 18,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,12</t>
+          <t>10,06; 19,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 17,23</t>
+          <t>12,93; 17,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,64; 25,76</t>
+          <t>21,4; 25,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,6; 31,79</t>
+          <t>25,68; 31,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,66; 24,66</t>
+          <t>19,66; 24,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,93</t>
+          <t>20,46; 23,94</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,41</t>
+          <t>20,53</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,63</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,08</t>
+          <t>20,17</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,81; 27,38</t>
+          <t>21,87; 27,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,2; 26,13</t>
+          <t>21,11; 25,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,4</t>
+          <t>20,39; 25,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,54; 22,34</t>
+          <t>18,71; 22,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 19,26</t>
+          <t>8,97; 19,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,84</t>
+          <t>6,88; 17,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,07; 22,95</t>
+          <t>13,28; 22,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 25,92</t>
+          <t>21,23; 26,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,81; 25,46</t>
+          <t>20,68; 25,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,43</t>
+          <t>20,26; 25,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,43; 21,98</t>
+          <t>18,34; 22,08</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,51</t>
+          <t>20,56</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,17</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,36; 23,45</t>
+          <t>21,37; 23,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,08; 24,29</t>
+          <t>22,06; 24,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 22,81</t>
+          <t>20,49; 22,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,55</t>
+          <t>19,54; 21,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,64; 13,87</t>
+          <t>11,5; 13,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,52</t>
+          <t>12,42; 14,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,49</t>
+          <t>12,36; 14,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,09</t>
+          <t>11,51; 13,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,59</t>
+          <t>18,73; 20,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,9</t>
+          <t>19,21; 21,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,66; 19,54</t>
+          <t>17,85; 19,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,12</t>
+          <t>16,91; 18,44</t>
         </is>
       </c>
     </row>
